--- a/data/outputs/Data_Figure_4.xlsx
+++ b/data/outputs/Data_Figure_4.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\01_3rd_submission\Manuscript_datasets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PAISBA\Documents\01_Post-doc\02_Articles\00_Article_1\00_Nature_Communications\02_Final_revision\0_Final_submission\Manuscript_datasets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0691299-C1AD-49FF-A00A-E7F287217E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FABB0C80-2DCA-4E9E-B90E-E228F6ADD252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25320" yWindow="2175" windowWidth="25440" windowHeight="15270" xr2:uid="{2606B934-8CA6-4691-A232-42A0D7768048}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{2606B934-8CA6-4691-A232-42A0D7768048}"/>
   </bookViews>
   <sheets>
-    <sheet name="Fig 4" sheetId="2" r:id="rId1"/>
+    <sheet name="Figure 4" sheetId="2" r:id="rId1"/>
     <sheet name="Absolute values" sheetId="1" r:id="rId2"/>
     <sheet name="Values relative to IAM" sheetId="3" r:id="rId3"/>
     <sheet name="Values relative to baseline" sheetId="4" r:id="rId4"/>
@@ -131,14 +131,14 @@
     <t>Values relative to IAM</t>
   </si>
   <si>
-    <t>Data displayed in Fig 4
+    <t>Data displayed in Figure 4 
+Results sensitivity to choice of IAM-SSP-RCP
+Results are displayed in absolute terms (unit)</t>
+  </si>
+  <si>
+    <t>Data displayed in Figure 4
 Results sensitivity to choice of IAM-SSP-RCP
 Results are displayed in relative terms (% of resource in underlying scenario)</t>
-  </si>
-  <si>
-    <t>Data displayed in Fig 4 
-Results sensitivity to choice of IAM-SSP-RCP
-Results are displayed in absolute terms (unit)</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1087,7 @@
         <v>27</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
@@ -1095,7 +1095,7 @@
         <v>29</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
